--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486767_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486767_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4713</v>
+        <v>1.6605</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3441</v>
+        <v>2.6823</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8728</v>
+        <v>-1.0218</v>
       </c>
       <c r="G2" t="n">
         <v>-0.09130000000000001</v>
@@ -610,13 +610,13 @@
         <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7557</v>
+        <v>-0.0551</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5236</v>
+        <v>-0.1383</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2321</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>1.2277</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2891</v>
+        <v>0.9317</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3977</v>
+        <v>0.4436</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6868</v>
+        <v>0.4881</v>
       </c>
       <c r="G3" t="n">
         <v>2.0801</v>
@@ -688,13 +688,13 @@
         <v>2.3169</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7943</v>
+        <v>-0.1517</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4624</v>
+        <v>-0.6211</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6681</v>
+        <v>0.4695</v>
       </c>
       <c r="V3" t="n">
         <v>1.5133</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1684</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>-0.9447</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7763</v>
+        <v>0.8756</v>
       </c>
       <c r="G4" t="n">
         <v>0.2342</v>
@@ -766,13 +766,13 @@
         <v>0.3862</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.6895</v>
       </c>
       <c r="T4" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5129</v>
+        <v>-0.4136</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6472</v>
+        <v>-0.3106</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8274</v>
+        <v>-0.5654</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1803</v>
+        <v>0.2548</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4139</v>
@@ -844,13 +844,13 @@
         <v>1.1585</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3917</v>
+        <v>-0.0552</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2207</v>
+        <v>0.0413</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1709</v>
+        <v>-0.0965</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7694</v>
+        <v>-0.4893</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8538</v>
+        <v>-0.8469</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0844</v>
+        <v>0.3575</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9789</v>
@@ -922,13 +922,13 @@
         <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1766</v>
+        <v>0.1035</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0555</v>
+        <v>-0.0486</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1211</v>
+        <v>0.152</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4703</v>
+        <v>-1.4206</v>
       </c>
       <c r="E7" t="n">
         <v>-1.7445</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2743</v>
+        <v>0.324</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3174</v>
@@ -1000,13 +1000,13 @@
         <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5737</v>
+        <v>-0.524</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4633</v>
+        <v>-0.4136</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5031</v>
+        <v>-1.4783</v>
       </c>
       <c r="E8" t="n">
         <v>-0.1812</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3219</v>
+        <v>-1.2971</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8095</v>
@@ -1078,13 +1078,13 @@
         <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7282</v>
+        <v>-0.7034</v>
       </c>
       <c r="T8" t="n">
         <v>-0.607</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1212</v>
+        <v>-0.0964</v>
       </c>
       <c r="V8" t="n">
         <v>1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9536</v>
+        <v>-2.7221</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4833</v>
+        <v>-1.9041</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4704</v>
+        <v>-0.8179999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9348</v>
@@ -1156,13 +1156,13 @@
         <v>1.3515</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7831</v>
+        <v>-0.5515</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5451</v>
+        <v>-0.9659</v>
       </c>
       <c r="U9" t="n">
-        <v>0.762</v>
+        <v>0.4143</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6565</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.717</v>
+        <v>-4.4054</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3906</v>
+        <v>-3.1286</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3264</v>
+        <v>-1.2768</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2401</v>
@@ -1234,13 +1234,13 @@
         <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5461</v>
+        <v>-0.2344</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6347</v>
+        <v>-0.3726</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0885</v>
+        <v>0.1382</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2277</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7732</v>
+        <v>-5.8353</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.8355</v>
+        <v>-5.7734</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0623</v>
+        <v>-0.0618</v>
       </c>
       <c r="G11" t="n">
         <v>-8.0435</v>
@@ -1312,13 +1312,13 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>0.193</v>
+        <v>0.131</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4418</v>
+        <v>-0.3797</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6348</v>
+        <v>0.5107</v>
       </c>
       <c r="V11" t="n">
         <v>1.8842</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9279</v>
+        <v>-5.9277</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8368</v>
+        <v>-5.085</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.091</v>
+        <v>-0.8427</v>
       </c>
       <c r="G12" t="n">
         <v>-5.6242</v>
@@ -1390,13 +1390,13 @@
         <v>1.9308</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3037</v>
+        <v>-0.3035</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.2487</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3031</v>
+        <v>-0.0548</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.1697</v>
+        <v>-20.0662</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.1514</v>
+        <v>-17.0479</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0181</v>
+        <v>-3.018199999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-17.1393</v>
@@ -1468,13 +1468,13 @@
         <v>13.5155</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.137499999999999</v>
+        <v>-3.0338</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.8305</v>
+        <v>-3.7269</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6930000000000001</v>
+        <v>0.6929000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>3.9687</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.6824</v>
+        <v>5.7612</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9903</v>
+        <v>1.956</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6921</v>
+        <v>3.8052</v>
       </c>
       <c r="G14" t="n">
         <v>3.1807</v>
@@ -1546,13 +1546,13 @@
         <v>2.8962</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9418</v>
+        <v>1.0206</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9095</v>
+        <v>-0.1247</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0323</v>
+        <v>1.1453</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3709</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.6718</v>
+        <v>5.6843</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7544</v>
+        <v>1.927</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9174</v>
+        <v>3.7573</v>
       </c>
       <c r="G15" t="n">
         <v>1.9331</v>
@@ -1624,13 +1624,13 @@
         <v>2.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2286</v>
+        <v>1.2412</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9923</v>
+        <v>0.165</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2363</v>
+        <v>1.0762</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0193</v>
+        <v>4.5571</v>
       </c>
       <c r="E16" t="n">
-        <v>1.364</v>
+        <v>1.7777</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6553</v>
+        <v>2.7794</v>
       </c>
       <c r="G16" t="n">
         <v>3.6662</v>
@@ -1702,13 +1702,13 @@
         <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4965</v>
+        <v>0.0414</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0209</v>
+        <v>-0.6072</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5245</v>
+        <v>0.6486</v>
       </c>
       <c r="V16" t="n">
         <v>0.6565</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2643</v>
+        <v>2.8346</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2402</v>
+        <v>-0.1162</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5045</v>
+        <v>2.9507</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5649</v>
+        <v>0.7315</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7247</v>
+        <v>-0.0553</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8402</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1114</v>
+        <v>0.2359</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3118</v>
+        <v>-0.2616</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7996</v>
+        <v>0.4975</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4535</v>
+        <v>0.4956</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4129</v>
+        <v>0.2063</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0406</v>
+        <v>0.2893</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9654</v>
+        <v>1.9308</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8962</v>
+        <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0496</v>
+        <v>0.1723</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7177</v>
+        <v>-0.352</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6681</v>
+        <v>0.5243</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MIJE BENITEZ</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1783</v>
+        <v>2.4519</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5844</v>
+        <v>-0.2402</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5939</v>
+        <v>2.6921</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0461</v>
+        <v>3.5649</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3657</v>
+        <v>1.7247</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6804</v>
+        <v>1.8402</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4192</v>
+        <v>3.1114</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2971</v>
+        <v>1.3118</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1221</v>
+        <v>1.7996</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6269</v>
+        <v>0.4535</v>
       </c>
       <c r="N18" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.4129</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5583</v>
+        <v>0.0406</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5792</v>
+        <v>2.8962</v>
       </c>
       <c r="S18" t="n">
-        <v>1.804</v>
+        <v>0.138</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1306</v>
+        <v>-0.7177</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6734</v>
+        <v>0.8557</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2856</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2856</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>M. MIJE BENITEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0773</v>
+        <v>1.388</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4264</v>
+        <v>0.0673</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5038</v>
+        <v>1.3208</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7315</v>
+        <v>1.0461</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0553</v>
+        <v>0.3657</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.6804</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2359</v>
+        <v>0.4192</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2616</v>
+        <v>0.2971</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4975</v>
+        <v>0.1221</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4956</v>
+        <v>0.6269</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2063</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2893</v>
+        <v>0.5583</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9308</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9308</v>
+        <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5849</v>
+        <v>1.0137</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6623</v>
+        <v>0.6135</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0774</v>
+        <v>0.4002</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0478</v>
+        <v>0.6613</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2063</v>
+        <v>-0.4823</v>
       </c>
       <c r="F20" t="n">
-        <v>1.254</v>
+        <v>1.1436</v>
       </c>
       <c r="G20" t="n">
         <v>2.875</v>
@@ -2014,13 +2014,13 @@
         <v>2.3169</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0549</v>
+        <v>0.5586</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.745</v>
+        <v>-0.0211</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6901</v>
+        <v>0.5796</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2277</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6641</v>
+        <v>-0.3042</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.904</v>
+        <v>-0.5937</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2399</v>
+        <v>0.2895</v>
       </c>
       <c r="G21" t="n">
         <v>0.2682</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0331</v>
+        <v>0.393</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.3103</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1073</v>
+        <v>-1.175</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8979</v>
+        <v>-1.2774</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2094</v>
+        <v>0.1023</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1263</v>
@@ -2170,13 +2170,13 @@
         <v>2.1239</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6841</v>
+        <v>0.2482</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5795</v>
+        <v>0.0411</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1046</v>
+        <v>0.2071</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4554</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>21.1698</v>
+        <v>21.8592</v>
       </c>
       <c r="E23" t="n">
-        <v>3.0183</v>
+        <v>3.0182</v>
       </c>
       <c r="F23" t="n">
-        <v>18.1515</v>
+        <v>18.8409</v>
       </c>
       <c r="G23" t="n">
         <v>17.1394</v>
@@ -2248,13 +2248,13 @@
         <v>17.3771</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1375</v>
+        <v>4.827</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.6927999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>4.8306</v>
+        <v>5.519799999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-3.9687</v>
